--- a/NTu/Kabianga_Tea_results.xlsx
+++ b/NTu/Kabianga_Tea_results.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,32 +417,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>SOC Baseline (t/ha)</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>SOC Project (t/ha)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>SOC Difference (t/ha)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Delta SOC (t/ha)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>ERs (tCO2e/ha)</t>
         </is>
@@ -481,19 +469,19 @@
         <v>2026</v>
       </c>
       <c r="B3" t="n">
-        <v>99.1784031912734</v>
+        <v>103.7261320951452</v>
       </c>
       <c r="C3" t="n">
         <v>113.649862435789</v>
       </c>
       <c r="D3" t="n">
-        <v>14.47145924451563</v>
+        <v>9.923730340643857</v>
       </c>
       <c r="E3" t="n">
-        <v>14.47159350669013</v>
+        <v>9.923864602818355</v>
       </c>
       <c r="F3" t="n">
-        <v>53.06250952453047</v>
+        <v>36.3875035436673</v>
       </c>
     </row>
     <row r="4">
@@ -501,19 +489,19 @@
         <v>2027</v>
       </c>
       <c r="B4" t="n">
-        <v>91.57874159893765</v>
+        <v>98.52558556708217</v>
       </c>
       <c r="C4" t="n">
         <v>113.6498616437091</v>
       </c>
       <c r="D4" t="n">
-        <v>22.07112004477143</v>
+        <v>15.12427607662691</v>
       </c>
       <c r="E4" t="n">
-        <v>7.599660800255805</v>
+        <v>5.200545735983056</v>
       </c>
       <c r="F4" t="n">
-        <v>27.86542293427128</v>
+        <v>19.06866769860454</v>
       </c>
     </row>
     <row r="5">
@@ -521,19 +509,19 @@
         <v>2028</v>
       </c>
       <c r="B5" t="n">
-        <v>86.8139031333218</v>
+        <v>95.28179082709231</v>
       </c>
       <c r="C5" t="n">
         <v>113.6498609222855</v>
       </c>
       <c r="D5" t="n">
-        <v>26.8359577889637</v>
+        <v>18.36807009519319</v>
       </c>
       <c r="E5" t="n">
-        <v>4.764837744192263</v>
+        <v>3.243794018566277</v>
       </c>
       <c r="F5" t="n">
-        <v>17.47107172870497</v>
+        <v>11.89391140140968</v>
       </c>
     </row>
     <row r="6">
@@ -541,19 +529,19 @@
         <v>2029</v>
       </c>
       <c r="B6" t="n">
-        <v>83.56723359079699</v>
+        <v>93.09184486840562</v>
       </c>
       <c r="C6" t="n">
         <v>113.6498602652155</v>
       </c>
       <c r="D6" t="n">
-        <v>30.08262667441846</v>
+        <v>20.55801539680984</v>
       </c>
       <c r="E6" t="n">
-        <v>3.246668885454767</v>
+        <v>2.189945301616646</v>
       </c>
       <c r="F6" t="n">
-        <v>11.90445258000081</v>
+        <v>8.029799439261035</v>
       </c>
     </row>
     <row r="7">
@@ -561,19 +549,19 @@
         <v>2030</v>
       </c>
       <c r="B7" t="n">
-        <v>81.15665222173354</v>
+        <v>91.48701935134834</v>
       </c>
       <c r="C7" t="n">
         <v>113.6498596667584</v>
       </c>
       <c r="D7" t="n">
-        <v>32.49320744502488</v>
+        <v>22.16284031541008</v>
       </c>
       <c r="E7" t="n">
-        <v>2.410580770606416</v>
+        <v>1.604824918600244</v>
       </c>
       <c r="F7" t="n">
-        <v>8.83879615889019</v>
+        <v>5.88435803486756</v>
       </c>
     </row>
     <row r="8">
@@ -581,19 +569,19 @@
         <v>2031</v>
       </c>
       <c r="B8" t="n">
-        <v>79.2244038245812</v>
+        <v>90.22064318513694</v>
       </c>
       <c r="C8" t="n">
         <v>113.6498591216859</v>
       </c>
       <c r="D8" t="n">
-        <v>34.42545529710469</v>
+        <v>23.42921593654896</v>
       </c>
       <c r="E8" t="n">
-        <v>1.932247852079811</v>
+        <v>1.266375621138877</v>
       </c>
       <c r="F8" t="n">
-        <v>7.084908790959308</v>
+        <v>4.643377277509217</v>
       </c>
     </row>
     <row r="9">
@@ -601,19 +589,19 @@
         <v>2032</v>
       </c>
       <c r="B9" t="n">
-        <v>77.58083202203373</v>
+        <v>89.16127063739677</v>
       </c>
       <c r="C9" t="n">
         <v>113.6498586252358</v>
       </c>
       <c r="D9" t="n">
-        <v>36.06902660320208</v>
+        <v>24.48858798783904</v>
       </c>
       <c r="E9" t="n">
-        <v>1.643571306097385</v>
+        <v>1.059372051290083</v>
       </c>
       <c r="F9" t="n">
-        <v>6.026428122357079</v>
+        <v>3.884364188063638</v>
       </c>
     </row>
     <row r="10">
@@ -621,19 +609,19 @@
         <v>2033</v>
       </c>
       <c r="B10" t="n">
-        <v>76.12415657329142</v>
+        <v>88.23779228311186</v>
       </c>
       <c r="C10" t="n">
         <v>113.6498581730708</v>
       </c>
       <c r="D10" t="n">
-        <v>37.52570159977941</v>
+        <v>25.41206588995897</v>
       </c>
       <c r="E10" t="n">
-        <v>1.456674996577334</v>
+        <v>0.9234779021199273</v>
       </c>
       <c r="F10" t="n">
-        <v>5.341141654116892</v>
+        <v>3.3860856411064</v>
       </c>
     </row>
     <row r="11">
@@ -641,19 +629,19 @@
         <v>2034</v>
       </c>
       <c r="B11" t="n">
-        <v>74.79880045388829</v>
+        <v>87.41089859555071</v>
       </c>
       <c r="C11" t="n">
         <v>113.6498577612406</v>
       </c>
       <c r="D11" t="n">
-        <v>38.85105730735231</v>
+        <v>26.23895916568989</v>
       </c>
       <c r="E11" t="n">
-        <v>1.325355707572896</v>
+        <v>0.8268932757309244</v>
       </c>
       <c r="F11" t="n">
-        <v>4.859637594433953</v>
+        <v>3.03194201101339</v>
       </c>
     </row>
     <row r="12">
@@ -661,19 +649,19 @@
         <v>2035</v>
       </c>
       <c r="B12" t="n">
-        <v>73.57359552843258</v>
+        <v>86.65814015962053</v>
       </c>
       <c r="C12" t="n">
         <v>113.6498573861471</v>
       </c>
       <c r="D12" t="n">
-        <v>40.07626185771454</v>
+        <v>26.99171722652659</v>
       </c>
       <c r="E12" t="n">
-        <v>1.225204550362236</v>
+        <v>0.7527580608366975</v>
       </c>
       <c r="F12" t="n">
-        <v>4.492416684661531</v>
+        <v>2.760112889734557</v>
       </c>
     </row>
     <row r="13">
@@ -681,19 +669,19 @@
         <v>2036</v>
       </c>
       <c r="B13" t="n">
-        <v>72.43033800355127</v>
+        <v>85.96607221622651</v>
       </c>
       <c r="C13" t="n">
         <v>113.6498570445133</v>
       </c>
       <c r="D13" t="n">
-        <v>41.219519040962</v>
+        <v>27.68378482828676</v>
       </c>
       <c r="E13" t="n">
-        <v>1.143257183247457</v>
+        <v>0.6920676017601721</v>
       </c>
       <c r="F13" t="n">
-        <v>4.191943005240674</v>
+        <v>2.537581206453964</v>
       </c>
     </row>
     <row r="14">
@@ -701,19 +689,19 @@
         <v>2037</v>
       </c>
       <c r="B14" t="n">
-        <v>71.35776243836517</v>
+        <v>85.32611136861622</v>
       </c>
       <c r="C14" t="n">
         <v>113.6498567333544</v>
       </c>
       <c r="D14" t="n">
-        <v>42.29209429498918</v>
+        <v>28.32374536473813</v>
       </c>
       <c r="E14" t="n">
-        <v>1.072575254027186</v>
+        <v>0.639960536451369</v>
       </c>
       <c r="F14" t="n">
-        <v>3.932775931433014</v>
+        <v>2.346521966988353</v>
       </c>
     </row>
     <row r="15">
@@ -721,19 +709,19 @@
         <v>2038</v>
       </c>
       <c r="B15" t="n">
-        <v>70.34836175660362</v>
+        <v>84.73234392921897</v>
       </c>
       <c r="C15" t="n">
         <v>113.649856449952</v>
       </c>
       <c r="D15" t="n">
-        <v>43.30149469334833</v>
+        <v>28.91751252073298</v>
       </c>
       <c r="E15" t="n">
-        <v>1.009400398359148</v>
+        <v>0.5937671559948541</v>
       </c>
       <c r="F15" t="n">
-        <v>3.701134793983542</v>
+        <v>2.177146238647798</v>
       </c>
     </row>
     <row r="16">
@@ -741,19 +729,19 @@
         <v>2039</v>
       </c>
       <c r="B16" t="n">
-        <v>69.39670499780432</v>
+        <v>84.18036246826561</v>
       </c>
       <c r="C16" t="n">
         <v>113.64985619183</v>
       </c>
       <c r="D16" t="n">
-        <v>44.25315119402572</v>
+        <v>29.46949372356443</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9516565006773874</v>
+        <v>0.5519812028314419</v>
       </c>
       <c r="F16" t="n">
-        <v>3.48940716915042</v>
+        <v>2.023931077048621</v>
       </c>
     </row>
     <row r="17">
@@ -761,19 +749,19 @@
         <v>2040</v>
       </c>
       <c r="B17" t="n">
-        <v>68.49854431613208</v>
+        <v>83.66664488739913</v>
       </c>
       <c r="C17" t="n">
         <v>113.6498559567335</v>
       </c>
       <c r="D17" t="n">
-        <v>45.15131164060139</v>
+        <v>29.98321106933435</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8981604465756732</v>
+        <v>0.5137173457699191</v>
       </c>
       <c r="F17" t="n">
-        <v>3.293254970777468</v>
+        <v>1.883630267823037</v>
       </c>
     </row>
     <row r="18">
@@ -781,19 +769,19 @@
         <v>2041</v>
       </c>
       <c r="B18" t="n">
-        <v>67.65033834258774</v>
+        <v>83.18822016870458</v>
       </c>
       <c r="C18" t="n">
         <v>113.6498557426084</v>
       </c>
       <c r="D18" t="n">
-        <v>45.99951740002065</v>
+        <v>30.46163557390382</v>
       </c>
       <c r="E18" t="n">
-        <v>0.8482057594192582</v>
+        <v>0.4784245045694746</v>
       </c>
       <c r="F18" t="n">
-        <v>3.11008778453728</v>
+        <v>1.754223183421407</v>
       </c>
     </row>
     <row r="19">
@@ -801,19 +789,19 @@
         <v>2042</v>
       </c>
       <c r="B19" t="n">
-        <v>66.84899546620561</v>
+        <v>82.74248588018999</v>
       </c>
       <c r="C19" t="n">
         <v>113.6498555475841</v>
       </c>
       <c r="D19" t="n">
-        <v>46.80086008137846</v>
+        <v>30.90736966739408</v>
       </c>
       <c r="E19" t="n">
-        <v>0.8013426813578093</v>
+        <v>0.4457340934902589</v>
       </c>
       <c r="F19" t="n">
-        <v>2.938256498311967</v>
+        <v>1.634358342797616</v>
       </c>
     </row>
     <row r="20">
@@ -821,19 +809,19 @@
         <v>2043</v>
       </c>
       <c r="B20" t="n">
-        <v>66.09173347045153</v>
+        <v>82.32710623356333</v>
       </c>
       <c r="C20" t="n">
         <v>113.6498553699566</v>
       </c>
       <c r="D20" t="n">
-        <v>47.5581218995051</v>
+        <v>31.3227491363933</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7572618181266364</v>
+        <v>0.4153794689992196</v>
       </c>
       <c r="F20" t="n">
-        <v>2.776626666464333</v>
+        <v>1.523058052997139</v>
       </c>
     </row>
     <row r="21">
@@ -841,19 +829,19 @@
         <v>2044</v>
       </c>
       <c r="B21" t="n">
-        <v>65.37600089375407</v>
+        <v>81.93995308677722</v>
       </c>
       <c r="C21" t="n">
         <v>113.6498552081742</v>
       </c>
       <c r="D21" t="n">
-        <v>48.27385431442016</v>
+        <v>31.70990212139701</v>
       </c>
       <c r="E21" t="n">
-        <v>0.7157324149150668</v>
+        <v>0.3871529850037092</v>
       </c>
       <c r="F21" t="n">
-        <v>2.624352188021911</v>
+        <v>1.4195609450136</v>
       </c>
     </row>
     <row r="22">
@@ -861,19 +849,19 @@
         <v>2045</v>
       </c>
       <c r="B22" t="n">
-        <v>64.69943127622314</v>
+        <v>81.57907000897276</v>
       </c>
       <c r="C22" t="n">
         <v>113.6498550608233</v>
       </c>
       <c r="D22" t="n">
-        <v>48.95042378460019</v>
+        <v>32.07078505185056</v>
       </c>
       <c r="E22" t="n">
-        <v>0.6765694701800271</v>
+        <v>0.3608829304535561</v>
       </c>
       <c r="F22" t="n">
-        <v>2.480754723993433</v>
+        <v>1.323237411663039</v>
       </c>
     </row>
     <row r="23">
@@ -881,19 +869,19 @@
         <v>2046</v>
       </c>
       <c r="B23" t="n">
-        <v>64.05981505601358</v>
+        <v>81.24264888119392</v>
       </c>
       <c r="C23" t="n">
         <v>113.6498549266166</v>
       </c>
       <c r="D23" t="n">
-        <v>49.59003987060302</v>
+        <v>32.40720604542268</v>
       </c>
       <c r="E23" t="n">
-        <v>0.6396160860028317</v>
+        <v>0.3364209935721192</v>
       </c>
       <c r="F23" t="n">
-        <v>2.345258982010383</v>
+        <v>1.23354364309777</v>
       </c>
     </row>
     <row r="24">
@@ -901,19 +889,19 @@
         <v>2047</v>
       </c>
       <c r="B24" t="n">
-        <v>63.45508105383355</v>
+        <v>80.92901344665854</v>
       </c>
       <c r="C24" t="n">
         <v>113.6498548043817</v>
       </c>
       <c r="D24" t="n">
-        <v>50.19477375054812</v>
+        <v>32.72084135772313</v>
       </c>
       <c r="E24" t="n">
-        <v>0.6047338799451012</v>
+        <v>0.3136353123004483</v>
       </c>
       <c r="F24" t="n">
-        <v>2.217357559798705</v>
+        <v>1.149996145101644</v>
       </c>
     </row>
     <row r="25">
@@ -921,19 +909,19 @@
         <v>2048</v>
       </c>
       <c r="B25" t="n">
-        <v>62.88328327066734</v>
+        <v>80.63660683471097</v>
       </c>
       <c r="C25" t="n">
         <v>113.6498546930506</v>
       </c>
       <c r="D25" t="n">
-        <v>50.76657142238322</v>
+        <v>33.01324785833958</v>
       </c>
       <c r="E25" t="n">
-        <v>0.5717976718350926</v>
+        <v>0.2924065006164511</v>
       </c>
       <c r="F25" t="n">
-        <v>2.09659146339534</v>
+        <v>1.072157168926988</v>
       </c>
     </row>
     <row r="26">
@@ -941,19 +929,19 @@
         <v>2049</v>
       </c>
       <c r="B26" t="n">
-        <v>62.34259072322011</v>
+        <v>80.36398146293932</v>
       </c>
       <c r="C26" t="n">
         <v>113.6498545916505</v>
       </c>
       <c r="D26" t="n">
-        <v>51.30726386843041</v>
+        <v>33.2858731287112</v>
       </c>
       <c r="E26" t="n">
-        <v>0.5406924460471956</v>
+        <v>0.2726252703716199</v>
       </c>
       <c r="F26" t="n">
-        <v>1.982538968839717</v>
+        <v>0.9996259913626062</v>
       </c>
     </row>
     <row r="27">
@@ -961,19 +949,19 @@
         <v>2050</v>
       </c>
       <c r="B27" t="n">
-        <v>61.83127909823163</v>
+        <v>80.10979045283871</v>
       </c>
       <c r="C27" t="n">
         <v>113.6498544992957</v>
       </c>
       <c r="D27" t="n">
-        <v>51.8185754010641</v>
+        <v>33.54006404645702</v>
       </c>
       <c r="E27" t="n">
-        <v>0.511311532633691</v>
+        <v>0.2541909177458166</v>
       </c>
       <c r="F27" t="n">
-        <v>1.8748089529902</v>
+        <v>0.9320333650679942</v>
       </c>
     </row>
     <row r="28">
@@ -981,19 +969,19 @@
         <v>2051</v>
       </c>
       <c r="B28" t="n">
-        <v>61.3477235659279</v>
+        <v>79.87278008224065</v>
       </c>
       <c r="C28" t="n">
         <v>113.6498544151793</v>
       </c>
       <c r="D28" t="n">
-        <v>52.30213084925141</v>
+        <v>33.77707433293865</v>
       </c>
       <c r="E28" t="n">
-        <v>0.4835554481873032</v>
+        <v>0.2370102864816346</v>
       </c>
       <c r="F28" t="n">
-        <v>1.773036643353445</v>
+        <v>0.8690377170993268</v>
       </c>
     </row>
     <row r="29">
@@ -1001,19 +989,19 @@
         <v>2052</v>
       </c>
       <c r="B29" t="n">
-        <v>60.89039238936848</v>
+        <v>79.65178300426186</v>
       </c>
       <c r="C29" t="n">
         <v>113.6498543385664</v>
       </c>
       <c r="D29" t="n">
-        <v>52.75946194919791</v>
+        <v>33.99807133430453</v>
       </c>
       <c r="E29" t="n">
-        <v>0.4573310999465008</v>
+        <v>0.2209970013658733</v>
       </c>
       <c r="F29" t="n">
-        <v>1.676880699803836</v>
+        <v>0.8103223383415354</v>
       </c>
     </row>
     <row r="30">
@@ -1021,19 +1009,19 @@
         <v>2053</v>
       </c>
       <c r="B30" t="n">
-        <v>60.4578411242154</v>
+        <v>79.44571207316433</v>
       </c>
       <c r="C30" t="n">
         <v>113.6498542687876</v>
       </c>
       <c r="D30" t="n">
-        <v>53.19201314457217</v>
+        <v>34.20414219562323</v>
       </c>
       <c r="E30" t="n">
-        <v>0.4325511953742591</v>
+        <v>0.2060708613187074</v>
       </c>
       <c r="F30" t="n">
-        <v>1.586021049705617</v>
+        <v>0.755593158168594</v>
       </c>
     </row>
     <row r="31">
@@ -1041,19 +1029,19 @@
         <v>2054</v>
       </c>
       <c r="B31" t="n">
-        <v>60.0487072878939</v>
+        <v>79.2535546773688</v>
       </c>
       <c r="C31" t="n">
         <v>113.6498542052333</v>
       </c>
       <c r="D31" t="n">
-        <v>53.60114691733941</v>
+        <v>34.39629952786451</v>
       </c>
       <c r="E31" t="n">
-        <v>0.4091337727672482</v>
+        <v>0.1921573322412797</v>
       </c>
       <c r="F31" t="n">
-        <v>1.500157166813243</v>
+        <v>0.7045768848846924</v>
       </c>
     </row>
     <row r="32">
@@ -1061,19 +1049,19 @@
         <v>2055</v>
       </c>
       <c r="B32" t="n">
-        <v>59.66170542274622</v>
+        <v>79.07436751276249</v>
       </c>
       <c r="C32" t="n">
         <v>113.6498541473483</v>
       </c>
       <c r="D32" t="n">
-        <v>53.98814872460212</v>
+        <v>34.57548663458584</v>
       </c>
       <c r="E32" t="n">
-        <v>0.3870018072627062</v>
+        <v>0.1791871067213293</v>
       </c>
       <c r="F32" t="n">
-        <v>1.419006626629923</v>
+        <v>0.6570193913115409</v>
       </c>
     </row>
     <row r="33">
@@ -1081,19 +1069,19 @@
         <v>2056</v>
       </c>
       <c r="B33" t="n">
-        <v>59.29562250282905</v>
+        <v>78.90727174798558</v>
       </c>
       <c r="C33" t="n">
         <v>113.6498540946269</v>
       </c>
       <c r="D33" t="n">
-        <v>54.35423159179781</v>
+        <v>34.74258234664129</v>
       </c>
       <c r="E33" t="n">
-        <v>0.3660828671956935</v>
+        <v>0.1670957120554419</v>
       </c>
       <c r="F33" t="n">
-        <v>1.342303846384209</v>
+        <v>0.6126842775366205</v>
       </c>
     </row>
     <row r="34">
@@ -1101,19 +1089,19 @@
         <v>2057</v>
       </c>
       <c r="B34" t="n">
-        <v>58.94931364809398</v>
+        <v>78.7514485442366</v>
       </c>
       <c r="C34" t="n">
         <v>113.6498540466084</v>
       </c>
       <c r="D34" t="n">
-        <v>54.7005403985144</v>
+        <v>34.89840550237179</v>
       </c>
       <c r="E34" t="n">
-        <v>0.3463088067165856</v>
+        <v>0.1558231557305021</v>
       </c>
       <c r="F34" t="n">
-        <v>1.269798957960814</v>
+        <v>0.571351571011841</v>
       </c>
     </row>
     <row r="35">
@@ -1121,19 +1109,19 @@
         <v>2058</v>
       </c>
       <c r="B35" t="n">
-        <v>58.62169811791934</v>
+        <v>78.6061348988362</v>
       </c>
       <c r="C35" t="n">
         <v>113.6498540028733</v>
       </c>
       <c r="D35" t="n">
-        <v>55.02815588495395</v>
+        <v>35.04371910403708</v>
       </c>
       <c r="E35" t="n">
-        <v>0.327615486439548</v>
+        <v>0.1453136016652934</v>
       </c>
       <c r="F35" t="n">
-        <v>1.201256783611676</v>
+        <v>0.5328165394394091</v>
       </c>
     </row>
     <row r="36">
@@ -1141,19 +1129,19 @@
         <v>2059</v>
       </c>
       <c r="B36" t="n">
-        <v>58.31175556101722</v>
+        <v>78.47061978620447</v>
       </c>
       <c r="C36" t="n">
         <v>113.6498539630395</v>
       </c>
       <c r="D36" t="n">
-        <v>55.33809840202228</v>
+        <v>35.17923417683504</v>
       </c>
       <c r="E36" t="n">
-        <v>0.3099425170683361</v>
+        <v>0.1355150727979577</v>
       </c>
       <c r="F36" t="n">
-        <v>1.136455895917232</v>
+        <v>0.4968886002591783</v>
       </c>
     </row>
     <row r="37">
@@ -1161,19 +1149,19 @@
         <v>2060</v>
       </c>
       <c r="B37" t="n">
-        <v>58.01852250206097</v>
+        <v>78.34424057304044</v>
       </c>
       <c r="C37" t="n">
         <v>113.6498539267591</v>
       </c>
       <c r="D37" t="n">
-        <v>55.63133142469808</v>
+        <v>35.30561335371861</v>
       </c>
       <c r="E37" t="n">
-        <v>0.2932330226757998</v>
+        <v>0.1263791768835745</v>
       </c>
       <c r="F37" t="n">
-        <v>1.075187749811266</v>
+        <v>0.4633903152397731</v>
       </c>
     </row>
     <row r="38">
@@ -1181,19 +1169,19 @@
         <v>2061</v>
       </c>
       <c r="B38" t="n">
-        <v>57.74108904771954</v>
+        <v>78.2263796868789</v>
       </c>
       <c r="C38" t="n">
         <v>113.6498538937149</v>
       </c>
       <c r="D38" t="n">
-        <v>55.90876484599539</v>
+        <v>35.42347420683603</v>
       </c>
       <c r="E38" t="n">
-        <v>0.2774334212973102</v>
+        <v>0.1178608531174206</v>
       </c>
       <c r="F38" t="n">
-        <v>1.017255878090137</v>
+        <v>0.432156461430542</v>
       </c>
     </row>
     <row r="39">
@@ -1201,19 +1189,19 @@
         <v>2062</v>
       </c>
       <c r="B39" t="n">
-        <v>57.47859579656102</v>
+        <v>78.116461519125</v>
       </c>
       <c r="C39" t="n">
         <v>113.6498538636185</v>
       </c>
       <c r="D39" t="n">
-        <v>56.17125806705752</v>
+        <v>35.53339234449355</v>
       </c>
       <c r="E39" t="n">
-        <v>0.2624932210621296</v>
+        <v>0.109918137657516</v>
       </c>
       <c r="F39" t="n">
-        <v>0.9624751438944751</v>
+        <v>0.4030331714108921</v>
       </c>
     </row>
     <row r="40">
@@ -1221,19 +1209,19 @@
         <v>2063</v>
       </c>
       <c r="B40" t="n">
-        <v>57.23023093871421</v>
+        <v>78.01394954529742</v>
       </c>
       <c r="C40" t="n">
         <v>113.6498538362068</v>
       </c>
       <c r="D40" t="n">
-        <v>56.41962289749258</v>
+        <v>35.63590429090937</v>
       </c>
       <c r="E40" t="n">
-        <v>0.2483648304350581</v>
+        <v>0.1025119464158166</v>
       </c>
       <c r="F40" t="n">
-        <v>0.9106710449285463</v>
+        <v>0.3758771368579943</v>
       </c>
     </row>
     <row r="41">
@@ -1241,19 +1229,19 @@
         <v>2064</v>
       </c>
       <c r="B41" t="n">
-        <v>56.99522753237749</v>
+        <v>77.91834364662782</v>
       </c>
       <c r="C41" t="n">
         <v>113.6498538112403</v>
       </c>
       <c r="D41" t="n">
-        <v>56.65462627886283</v>
+        <v>35.7315101646125</v>
       </c>
       <c r="E41" t="n">
-        <v>0.2350033813702481</v>
+        <v>0.09560587370313556</v>
       </c>
       <c r="F41" t="n">
-        <v>0.8616790650242431</v>
+        <v>0.3505548702448304</v>
       </c>
     </row>
     <row r="42">
@@ -1261,19 +1249,19 @@
         <v>2065</v>
       </c>
       <c r="B42" t="n">
-        <v>56.77286094530842</v>
+        <v>77.82917761842752</v>
       </c>
       <c r="C42" t="n">
         <v>113.6498537885009</v>
       </c>
       <c r="D42" t="n">
-        <v>56.8769928431925</v>
+        <v>35.8206761700734</v>
       </c>
       <c r="E42" t="n">
-        <v>0.2223665643296755</v>
+        <v>0.08916600546089626</v>
       </c>
       <c r="F42" t="n">
-        <v>0.8153440692088102</v>
+        <v>0.3269420200232863</v>
       </c>
     </row>
   </sheetData>
